--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,48 +1128,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>915699</v>
+        <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>100387</v>
+        <v>92173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2082</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väg mellan Stornässundet &amp; Saxnäs, Ås lm</t>
+          <t>Fiskonbäckdalen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>508918</v>
+        <v>510213</v>
       </c>
       <c r="R6" t="n">
-        <v>7209120</v>
+        <v>7207309</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-08-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2000-08-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Norra vägkanten mot sjön, örtrikt.</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,24 +1213,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonas F Grahn</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Näslund</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/915699</t>
+          <t>https://artportalen.se/Sighting/137355469</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>915706</v>
+        <v>915699</v>
       </c>
       <c r="B7" t="n">
         <v>100387</v>
@@ -1270,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510003</v>
+        <v>508918</v>
       </c>
       <c r="R7" t="n">
-        <v>7207991</v>
+        <v>7209120</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1300,17 +1295,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2000-08-13</t>
+          <t>2000-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2000-08-13</t>
+          <t>2000-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Båda sidor om vägkant, nordsida mer örter och skogsrör.</t>
+          <t>Norra vägkanten mot sjön, örtrikt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,51 +1331,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/915706</t>
+          <t>https://artportalen.se/Sighting/915699</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207089</v>
+        <v>915706</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>100387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2082</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Väg mellan Stornässundet &amp; Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510144</v>
+        <v>510003</v>
       </c>
       <c r="R8" t="n">
-        <v>7207312</v>
+        <v>7207991</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1407,22 +1402,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2000-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2000-08-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Båda sidor om vägkant, nordsida mer örter och skogsrör.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,24 +1427,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Peter Näslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207089</t>
+          <t>https://artportalen.se/Sighting/915706</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130207093</v>
+        <v>130207089</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1489,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510310</v>
+        <v>510144</v>
       </c>
       <c r="R9" t="n">
-        <v>7207347</v>
+        <v>7207312</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1524,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,56 +1550,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207093</t>
+          <t>https://artportalen.se/Sighting/130207089</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130207078</v>
+        <v>130207093</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510693</v>
+        <v>510310</v>
       </c>
       <c r="R10" t="n">
-        <v>7207626</v>
+        <v>7207347</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1641,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,13 +1662,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207078</t>
+          <t>https://artportalen.se/Sighting/130207093</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130207084</v>
+        <v>130207078</v>
       </c>
       <c r="B11" t="n">
         <v>57953</v>
@@ -1714,7 +1699,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1723,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510025</v>
+        <v>510693</v>
       </c>
       <c r="R11" t="n">
-        <v>7207259</v>
+        <v>7207626</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1753,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,13 +1779,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207084</t>
+          <t>https://artportalen.se/Sighting/130207078</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130207091</v>
+        <v>130207084</v>
       </c>
       <c r="B12" t="n">
         <v>57953</v>
@@ -1831,7 +1816,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1840,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510219</v>
+        <v>510025</v>
       </c>
       <c r="R12" t="n">
-        <v>7207326</v>
+        <v>7207259</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1870,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1911,13 +1896,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207091</t>
+          <t>https://artportalen.se/Sighting/130207084</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130207092</v>
+        <v>130207091</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -1948,7 +1933,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1957,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510260</v>
+        <v>510219</v>
       </c>
       <c r="R13" t="n">
-        <v>7207346</v>
+        <v>7207326</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,13 +2013,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207092</t>
+          <t>https://artportalen.se/Sighting/130207091</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130207097</v>
+        <v>130207092</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -2074,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510606</v>
+        <v>510260</v>
       </c>
       <c r="R14" t="n">
-        <v>7207462</v>
+        <v>7207346</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,16 +2130,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130207097</t>
+          <t>https://artportalen.se/Sighting/130207092</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>94152331</v>
+        <v>130207097</v>
       </c>
       <c r="B15" t="n">
-        <v>57020</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,16 +2147,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Clangula hyemalis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2179,28 +2164,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
+          <t>Fiskonbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>508202</v>
+        <v>510606</v>
       </c>
       <c r="R15" t="n">
-        <v>7209767</v>
+        <v>7207462</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2227,22 +2206,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,44 +2236,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94152331</t>
+          <t>https://artportalen.se/Sighting/130207097</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123675716</v>
+        <v>94152331</v>
       </c>
       <c r="B16" t="n">
-        <v>57132</v>
+        <v>57020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>102108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Alfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Clangula hyemalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2304,24 +2283,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kultsjön, Ås lm</t>
+          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509043</v>
+        <v>508202</v>
       </c>
       <c r="R16" t="n">
-        <v>7208879</v>
+        <v>7209767</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2348,22 +2329,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,27 +2359,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123675716</t>
+          <t>https://artportalen.se/Sighting/94152331</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130207082</v>
+        <v>123675716</v>
       </c>
       <c r="B17" t="n">
-        <v>99456</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,34 +2387,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510217</v>
+        <v>509043</v>
       </c>
       <c r="R17" t="n">
-        <v>7207322</v>
+        <v>7208879</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2460,22 +2450,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,6 +2490,118 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123675716</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130207082</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fiskonbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>510217</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7207322</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130207082</t>
         </is>
@@ -2523,6 +2625,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60737-2024 artfynd.xlsx
+++ b/artfynd/A 60737-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,7 +1131,7 @@
         <v>137355469</v>
       </c>
       <c r="B6" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>94152331</v>
+        <v>137544592</v>
       </c>
       <c r="B16" t="n">
-        <v>57020</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clangula hyemalis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2281,31 +2281,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
+          <t>Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>508202</v>
+        <v>510601</v>
       </c>
       <c r="R16" t="n">
-        <v>7209767</v>
+        <v>7207467</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,22 +2318,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-06-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, tretåig hackspett</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,44 +2353,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Evelina Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Sivencrona</t>
+          <t>Evelina Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94152331</t>
+          <t>https://artportalen.se/Sighting/137544592</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123675716</v>
+        <v>94152331</v>
       </c>
       <c r="B17" t="n">
-        <v>57132</v>
+        <v>57020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>102108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Alfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Clangula hyemalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2406,24 +2400,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kultsjön, Ås lm</t>
+          <t>Fiskonbäcken 39, Vilhelmina, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509043</v>
+        <v>508202</v>
       </c>
       <c r="R17" t="n">
-        <v>7208879</v>
+        <v>7209767</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,22 +2446,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,27 +2476,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Håkan Sivencrona</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123675716</t>
+          <t>https://artportalen.se/Sighting/94152331</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130207082</v>
+        <v>123675716</v>
       </c>
       <c r="B18" t="n">
-        <v>99456</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,34 +2504,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fiskonbäcken, Ås lm</t>
+          <t>Kultsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510217</v>
+        <v>509043</v>
       </c>
       <c r="R18" t="n">
-        <v>7207322</v>
+        <v>7208879</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,22 +2567,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,7 +2608,236 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/123675716</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130207082</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fiskonbäcken, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>510217</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7207322</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/130207082</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137544593</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92581</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Saxnäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>510601</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7207467</v>
+      </c>
+      <c r="S20" t="n">
+        <v>42</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammal kötticka</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evelina Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evelina Nilsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137544593</t>
         </is>
       </c>
     </row>
@@ -2626,6 +2860,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
